--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486559_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486559_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.349</v>
+        <v>8.194000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1193</v>
+        <v>5.9643</v>
       </c>
       <c r="F2" t="n">
         <v>2.2297</v>
@@ -610,10 +610,10 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6525</v>
+        <v>0.4975</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3461</v>
+        <v>0.1911</v>
       </c>
       <c r="U2" t="n">
         <v>0.3064</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6627</v>
+        <v>6.291</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0855</v>
+        <v>3.7755</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5771</v>
+        <v>2.5155</v>
       </c>
       <c r="G3" t="n">
         <v>3.8472</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9455</v>
+        <v>0.5738</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3377</v>
+        <v>0.0277</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6078</v>
+        <v>0.5462</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3348</v>
+        <v>4.1066</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9149</v>
+        <v>3.8717</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4199</v>
+        <v>0.235</v>
       </c>
       <c r="G4" t="n">
         <v>2.0655</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.736</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2896</v>
+        <v>0.2464</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6746</v>
+        <v>0.4897</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0487</v>
+        <v>3.3025</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0335</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0153</v>
+        <v>2.3988</v>
       </c>
       <c r="G5" t="n">
         <v>1.5241</v>
@@ -844,13 +844,13 @@
         <v>3.0451</v>
       </c>
       <c r="S5" t="n">
-        <v>1.132</v>
+        <v>0.3857</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3268</v>
+        <v>-0.4566</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4588</v>
+        <v>0.8424</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5649999999999999</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1093</v>
+        <v>0.9543</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7491</v>
+        <v>0.5941</v>
       </c>
       <c r="F6" t="n">
         <v>0.3602</v>
@@ -922,10 +922,10 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5275</v>
+        <v>0.3725</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2211</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U6" t="n">
         <v>0.3064</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4053</v>
+        <v>0.4361</v>
       </c>
       <c r="E7" t="n">
         <v>0.0182</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3871</v>
+        <v>0.4179</v>
       </c>
       <c r="G7" t="n">
         <v>0.1673</v>
@@ -1000,13 +1000,13 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.149</v>
+        <v>-0.121</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0244</v>
+        <v>-1.3971</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8754</v>
+        <v>1.2761</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4592</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8649</v>
+        <v>0.1631</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6044</v>
+        <v>0.0228</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2604</v>
+        <v>0.1403</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1686</v>
+        <v>-1.223</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4195</v>
+        <v>-2.0813</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.588</v>
+        <v>0.8582</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0527</v>
+        <v>-0.3538</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6175</v>
+        <v>0.8303</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6702</v>
+        <v>-1.1841</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8661</v>
+        <v>-0.5936</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7514</v>
+        <v>0.5506</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1147</v>
+        <v>-1.1442</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9188</v>
+        <v>0.2398</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1339</v>
+        <v>0.2796</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7849</v>
+        <v>-0.0399</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3839</v>
+        <v>-0.1742</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0106</v>
+        <v>-0.4002</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3732</v>
+        <v>0.2259</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0647</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0561</v>
+        <v>-1.4113</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.399</v>
+        <v>-2.97</v>
       </c>
       <c r="F11" t="n">
-        <v>1.343</v>
+        <v>1.5587</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5753</v>
@@ -1312,13 +1312,13 @@
         <v>2.6101</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2431</v>
+        <v>0.4017</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5444</v>
+        <v>-0.1153</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3013</v>
+        <v>0.517</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1654</v>
+        <v>-1.6271</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7771</v>
+        <v>0.0842</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6117</v>
+        <v>-1.7113</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3538</v>
+        <v>-0.0527</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8303</v>
+        <v>0.6175</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1841</v>
+        <v>-0.6702</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5936</v>
+        <v>0.8661</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5506</v>
+        <v>0.7514</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1442</v>
+        <v>0.1147</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2398</v>
+        <v>-0.9188</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2796</v>
+        <v>-0.1339</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0399</v>
+        <v>-0.7849</v>
       </c>
       <c r="P12" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1166</v>
+        <v>0.9253</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0959</v>
+        <v>0.6754</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0207</v>
+        <v>0.2499</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>-2.0647</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7227</v>
+        <v>-4.2265</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7688</v>
+        <v>-2.365</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9539</v>
+        <v>-1.8614</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8889</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7038</v>
+        <v>-0.2076</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0189</v>
+        <v>0.0736</v>
       </c>
       <c r="V13" t="n">
         <v>-1.13</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.797</v>
+        <v>14.8246</v>
       </c>
       <c r="E14" t="n">
-        <v>5.370699999999998</v>
+        <v>6.398299999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>8.426500000000001</v>
+        <v>8.426400000000001</v>
       </c>
       <c r="G14" t="n">
         <v>3.244200000000002</v>
@@ -1525,7 +1525,7 @@
         <v>8.488199999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3986000000000001</v>
+        <v>0.3986000000000005</v>
       </c>
       <c r="M14" t="n">
         <v>-5.6427</v>
@@ -1546,13 +1546,13 @@
         <v>19.5757</v>
       </c>
       <c r="S14" t="n">
-        <v>2.697699999999999</v>
+        <v>3.725199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0514</v>
+        <v>-0.02379999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.749</v>
+        <v>3.7492</v>
       </c>
       <c r="V14" t="n">
         <v>-3.0202</v>
@@ -1561,7 +1561,7 @@
         <v>6.235599999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.255899999999999</v>
+        <v>-9.2559</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1661</v>
+        <v>3.6454</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4625</v>
+        <v>3.5684</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7037</v>
+        <v>0.077</v>
       </c>
       <c r="G15" t="n">
         <v>1.2573</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6065</v>
+        <v>1.0857</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.0721</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6403</v>
+        <v>1.0136</v>
       </c>
       <c r="V15" t="n">
         <v>2.8249</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5169</v>
+        <v>2.1411</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8754</v>
+        <v>3.0989</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3585</v>
+        <v>-0.9578</v>
       </c>
       <c r="G16" t="n">
         <v>0.7978</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5859</v>
+        <v>-0.9617</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1404</v>
+        <v>-0.9169</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4455</v>
+        <v>-0.0448</v>
       </c>
       <c r="V16" t="n">
         <v>0.5649999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4198</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8315</v>
+        <v>-2.1829</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4117</v>
+        <v>2.094</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0051</v>
+        <v>-0.9871</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0037</v>
+        <v>-1.1864</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0088</v>
+        <v>0.1992</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2133</v>
+        <v>-1.6085</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3039</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5172</v>
+        <v>-0.9729</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2082</v>
+        <v>0.6214</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6998</v>
+        <v>-0.5508</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4916</v>
+        <v>1.1722</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9025</v>
+        <v>-0.4068</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1526</v>
+        <v>-0.5744</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7498</v>
+        <v>0.1676</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7696</v>
+        <v>-0.3742</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4064</v>
+        <v>-1.0293</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6368</v>
+        <v>0.6551</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9871</v>
+        <v>0.4487</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1864</v>
+        <v>0.3921</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1992</v>
+        <v>0.0566</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6085</v>
+        <v>0.405</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.3285</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9729</v>
+        <v>0.0765</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6214</v>
+        <v>0.0437</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5508</v>
+        <v>0.0636</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1722</v>
+        <v>-0.0199</v>
       </c>
       <c r="P18" t="n">
-        <v>1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0875</v>
+        <v>0.1601</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.3245</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2896</v>
+        <v>0.4846</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.113</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8649</v>
+        <v>-1.026</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2528</v>
+        <v>-2.2785</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3879</v>
+        <v>1.2525</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4487</v>
+        <v>0.0051</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3921</v>
+        <v>-1.0037</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0566</v>
+        <v>1.0088</v>
       </c>
       <c r="J19" t="n">
-        <v>0.405</v>
+        <v>0.2133</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3285</v>
+        <v>-0.3039</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0765</v>
+        <v>0.5172</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0437</v>
+        <v>-0.2082</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0636</v>
+        <v>-0.6998</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0199</v>
+        <v>0.4916</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.87</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3306</v>
+        <v>0.2962</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>-0.2944</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2174</v>
+        <v>0.5906</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.113</v>
+        <v>0.1952</v>
       </c>
       <c r="W19" t="n">
         <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.887</v>
+        <v>-1.0655</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5271</v>
+        <v>1.4154</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4141</v>
+        <v>-2.4808</v>
       </c>
       <c r="G20" t="n">
         <v>0.2569</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0309</v>
+        <v>-0.2094</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0225</v>
+        <v>-0.0892</v>
       </c>
       <c r="V20" t="n">
         <v>-0.678</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ANABITARTE SOROA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5945</v>
+        <v>-1.3779</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.882</v>
+        <v>0.7454</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7125</v>
+        <v>-2.1233</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.11</v>
+        <v>1.8928</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.11</v>
+        <v>-0.3559</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.2487</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7451</v>
+        <v>4.5075</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7451</v>
+        <v>1.0069</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.5006</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.365</v>
+        <v>-2.6147</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.365</v>
+        <v>-1.3628</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-1.2519</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-4.1326</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-4.5676</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.137</v>
+        <v>-0.155</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.137</v>
+        <v>-0.3245</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.1694</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.017</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>A. ANABITARTE SOROA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8737</v>
+        <v>-1.5945</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5219</v>
+        <v>-0.882</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3956</v>
+        <v>-0.7125</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8928</v>
+        <v>-1.11</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3559</v>
+        <v>-1.11</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2487</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5075</v>
+        <v>-0.7451</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0069</v>
+        <v>-0.7451</v>
       </c>
       <c r="L22" t="n">
-        <v>3.5006</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6147</v>
+        <v>-0.365</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3628</v>
+        <v>-0.365</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2519</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.1326</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5676</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6508</v>
+        <v>-0.137</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.548</v>
+        <v>-0.137</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1029</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.017</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.113</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6019</v>
+        <v>-2.1254</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5925</v>
+        <v>-1.4808</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0094</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3441</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0122</v>
+        <v>-0.5357</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4642</v>
+        <v>-0.0994</v>
       </c>
       <c r="V23" t="n">
         <v>2.1469</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0055</v>
+        <v>-2.8321</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1229</v>
+        <v>-2.0111</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8827</v>
+        <v>-0.821</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2761</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2689</v>
+        <v>-0.0955</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U24" t="n">
-        <v>0.005</v>
+        <v>0.0667</v>
       </c>
       <c r="V24" t="n">
         <v>-1.808</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.463200000000001</v>
+        <v>-7.6091</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7251</v>
+        <v>-7.3898</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7381</v>
+        <v>-0.2192</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1852</v>
@@ -2404,13 +2404,13 @@
         <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1029</v>
+        <v>-0.2488</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.5311</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2365</v>
+        <v>0.2824</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5649999999999999</v>
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.7971</v>
+        <v>-12.3071</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.426299999999999</v>
+        <v>-8.426300000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.3708</v>
+        <v>-3.8807</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2439</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.136800000000001</v>
+        <v>-8.136799999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>4.8927</v>
+        <v>4.892699999999998</v>
       </c>
       <c r="J26" t="n">
         <v>5.6427</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3513999999999997</v>
+        <v>0.3513999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>5.291299999999999</v>
@@ -2482,13 +2482,13 @@
         <v>8.700099999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6977</v>
+        <v>-1.2079</v>
       </c>
       <c r="T26" t="n">
         <v>-3.7493</v>
       </c>
       <c r="U26" t="n">
-        <v>1.0513</v>
+        <v>2.5415</v>
       </c>
       <c r="V26" t="n">
         <v>3.02</v>
